--- a/Team-Data/2008-09/4-1-2008-09.xlsx
+++ b/Team-Data/2008-09/4-1-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -760,7 +827,7 @@
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL2" t="n">
         <v>8</v>
@@ -775,13 +842,13 @@
         <v>23</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -793,13 +860,13 @@
         <v>21</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
@@ -808,7 +875,7 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>21</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -855,55 +922,55 @@
         <v>0.747</v>
       </c>
       <c r="H3" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J3" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.486</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="P3" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U3" t="n">
         <v>22.7</v>
       </c>
       <c r="V3" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W3" t="n">
         <v>7.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
@@ -915,10 +982,10 @@
         <v>22.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.1</v>
+        <v>100.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
         <v>2</v>
@@ -927,13 +994,13 @@
         <v>3</v>
       </c>
       <c r="AF3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -945,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AM3" t="n">
         <v>21</v>
@@ -954,13 +1021,13 @@
         <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP3" t="n">
         <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
         <v>21</v>
@@ -975,16 +1042,16 @@
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -1025,25 +1092,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4" t="n">
         <v>34</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>0.453</v>
+        <v>0.459</v>
       </c>
       <c r="H4" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="J4" t="n">
-        <v>76.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="K4" t="n">
         <v>0.457</v>
@@ -1055,28 +1122,28 @@
         <v>16.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.372</v>
+        <v>0.369</v>
       </c>
       <c r="O4" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P4" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Q4" t="n">
         <v>0.741</v>
       </c>
       <c r="R4" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="T4" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="U4" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V4" t="n">
         <v>15.7</v>
@@ -1085,7 +1152,7 @@
         <v>7.1</v>
       </c>
       <c r="X4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y4" t="n">
         <v>5.9</v>
@@ -1097,25 +1164,25 @@
         <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="AC4" t="n">
         <v>-0.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL4" t="n">
         <v>22</v>
@@ -1133,7 +1200,7 @@
         <v>22</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
         <v>26</v>
@@ -1145,10 +1212,10 @@
         <v>27</v>
       </c>
       <c r="AR4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
         <v>27</v>
@@ -1175,10 +1242,10 @@
         <v>13</v>
       </c>
       <c r="BB4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -1207,55 +1274,55 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" t="n">
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.467</v>
+        <v>0.474</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M5" t="n">
         <v>15.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O5" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="P5" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R5" t="n">
         <v>11.9</v>
       </c>
       <c r="S5" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="n">
         <v>21</v>
@@ -1276,19 +1343,19 @@
         <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>101.9</v>
+        <v>102</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.9</v>
+        <v>-0.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
@@ -1300,13 +1367,13 @@
         <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
       </c>
       <c r="AK5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL5" t="n">
         <v>23</v>
@@ -1315,13 +1382,13 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
@@ -1336,31 +1403,31 @@
         <v>8</v>
       </c>
       <c r="AU5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ5" t="n">
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
         <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -1389,25 +1456,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" t="n">
         <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.836</v>
+        <v>0.824</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.468</v>
@@ -1416,19 +1483,19 @@
         <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.389</v>
+        <v>0.387</v>
       </c>
       <c r="O6" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R6" t="n">
         <v>10.7</v>
@@ -1440,10 +1507,10 @@
         <v>42.1</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="W6" t="n">
         <v>7.5</v>
@@ -1455,19 +1522,19 @@
         <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1482,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1491,16 +1558,16 @@
         <v>6</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
         <v>6</v>
       </c>
       <c r="AN6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
@@ -1521,10 +1588,10 @@
         <v>23</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
         <v>6</v>
@@ -1536,7 +1603,7 @@
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
         <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="H7" t="n">
         <v>48.3</v>
@@ -1589,7 +1656,7 @@
         <v>38.1</v>
       </c>
       <c r="J7" t="n">
-        <v>82.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>0.46</v>
@@ -1598,7 +1665,7 @@
         <v>6.8</v>
       </c>
       <c r="M7" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="N7" t="n">
         <v>0.346</v>
@@ -1607,19 +1674,19 @@
         <v>18.2</v>
       </c>
       <c r="P7" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S7" t="n">
         <v>31.7</v>
       </c>
       <c r="T7" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U7" t="n">
         <v>21.5</v>
@@ -1649,7 +1716,7 @@
         <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1661,16 +1728,16 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ7" t="n">
         <v>6</v>
       </c>
       <c r="AK7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL7" t="n">
         <v>12</v>
@@ -1691,31 +1758,31 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
         <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
         <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
         <v>8</v>
       </c>
       <c r="AY7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA7" t="n">
         <v>24</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -1855,13 +1922,13 @@
         <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM8" t="n">
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1873,10 +1940,10 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT8" t="n">
         <v>13</v>
@@ -1894,7 +1961,7 @@
         <v>2</v>
       </c>
       <c r="AY8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ8" t="n">
         <v>26</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -1935,22 +2002,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E9" t="n">
         <v>36</v>
       </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>0.48</v>
+        <v>0.486</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
       </c>
       <c r="I9" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J9" t="n">
         <v>79.90000000000001</v>
@@ -1965,16 +2032,16 @@
         <v>12.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="O9" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P9" t="n">
         <v>22.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.752</v>
+        <v>0.75</v>
       </c>
       <c r="R9" t="n">
         <v>11.5</v>
@@ -1983,10 +2050,10 @@
         <v>29.7</v>
       </c>
       <c r="T9" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U9" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V9" t="n">
         <v>12</v>
@@ -2001,19 +2068,19 @@
         <v>4.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA9" t="n">
         <v>19.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.8</v>
+        <v>93.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
         <v>16</v>
@@ -2025,7 +2092,7 @@
         <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="n">
         <v>22</v>
@@ -2049,16 +2116,16 @@
         <v>29</v>
       </c>
       <c r="AP9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR9" t="n">
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT9" t="n">
         <v>17</v>
@@ -2085,10 +2152,10 @@
         <v>29</v>
       </c>
       <c r="BB9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
         <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>0.347</v>
+        <v>0.338</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>39.7</v>
+        <v>39.5</v>
       </c>
       <c r="J10" t="n">
-        <v>86.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L10" t="n">
         <v>6.7</v>
@@ -2147,13 +2214,13 @@
         <v>18</v>
       </c>
       <c r="N10" t="n">
-        <v>0.371</v>
+        <v>0.373</v>
       </c>
       <c r="O10" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="P10" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="Q10" t="n">
         <v>0.789</v>
@@ -2162,13 +2229,13 @@
         <v>11.6</v>
       </c>
       <c r="S10" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="T10" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U10" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V10" t="n">
         <v>14.9</v>
@@ -2183,19 +2250,19 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AA10" t="n">
         <v>23.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>109.1</v>
+        <v>108.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.8</v>
+        <v>-3.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,16 +2274,16 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AL10" t="n">
         <v>16</v>
@@ -2225,7 +2292,7 @@
         <v>17</v>
       </c>
       <c r="AN10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO10" t="n">
         <v>1</v>
@@ -2240,16 +2307,16 @@
         <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2267,7 +2334,7 @@
         <v>3</v>
       </c>
       <c r="BB10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC10" t="n">
         <v>24</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -2299,52 +2366,52 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E11" t="n">
         <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>0.64</v>
+        <v>0.649</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J11" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L11" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M11" t="n">
         <v>20.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.377</v>
+        <v>0.375</v>
       </c>
       <c r="O11" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P11" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R11" t="n">
         <v>10.4</v>
       </c>
       <c r="S11" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T11" t="n">
         <v>42.9</v>
@@ -2365,40 +2432,40 @@
         <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
         <v>7</v>
@@ -2407,13 +2474,13 @@
         <v>5</v>
       </c>
       <c r="AN11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
         <v>4</v>
@@ -2428,7 +2495,7 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV11" t="n">
         <v>16</v>
@@ -2449,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="BB11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
         <v>6</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -2577,19 +2644,19 @@
         <v>4</v>
       </c>
       <c r="AJ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL12" t="n">
         <v>3</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>4</v>
       </c>
       <c r="AM12" t="n">
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
         <v>22</v>
@@ -2619,7 +2686,7 @@
         <v>23</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
         <v>25</v>
@@ -2628,7 +2695,7 @@
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E13" t="n">
         <v>18</v>
       </c>
       <c r="F13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>0.24</v>
+        <v>0.243</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
@@ -2681,25 +2748,25 @@
         <v>36.1</v>
       </c>
       <c r="J13" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K13" t="n">
         <v>0.442</v>
       </c>
       <c r="L13" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M13" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="O13" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P13" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q13" t="n">
         <v>0.74</v>
@@ -2708,16 +2775,16 @@
         <v>10.9</v>
       </c>
       <c r="S13" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T13" t="n">
         <v>39.8</v>
       </c>
       <c r="U13" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V13" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W13" t="n">
         <v>6.9</v>
@@ -2729,19 +2796,19 @@
         <v>5.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="AC13" t="n">
         <v>-8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
@@ -2765,19 +2832,19 @@
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
         <v>16</v>
       </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="n">
         <v>28</v>
       </c>
       <c r="AP13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ13" t="n">
         <v>28</v>
@@ -2789,13 +2856,13 @@
         <v>25</v>
       </c>
       <c r="AT13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU13" t="n">
         <v>13</v>
       </c>
       <c r="AV13" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2810,7 +2877,7 @@
         <v>8</v>
       </c>
       <c r="BA13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -2863,49 +2930,49 @@
         <v>40.5</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="K14" t="n">
         <v>0.475</v>
       </c>
       <c r="L14" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M14" t="n">
         <v>18.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.362</v>
+        <v>0.364</v>
       </c>
       <c r="O14" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="P14" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="R14" t="n">
         <v>12.5</v>
       </c>
       <c r="S14" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T14" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U14" t="n">
         <v>23.4</v>
       </c>
       <c r="V14" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W14" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y14" t="n">
         <v>4.8</v>
@@ -2914,16 +2981,16 @@
         <v>20.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.3</v>
+        <v>107.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2950,7 +3017,7 @@
         <v>14</v>
       </c>
       <c r="AM14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
         <v>18</v>
@@ -2959,10 +3026,10 @@
         <v>12</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
@@ -2980,13 +3047,13 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ14" t="n">
         <v>12</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -3027,46 +3094,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F15" t="n">
         <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="J15" t="n">
         <v>77.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L15" t="n">
         <v>4.6</v>
       </c>
       <c r="M15" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O15" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P15" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R15" t="n">
         <v>10.5</v>
@@ -3078,16 +3145,16 @@
         <v>38.8</v>
       </c>
       <c r="U15" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="V15" t="n">
         <v>15.2</v>
       </c>
       <c r="W15" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
         <v>5.5</v>
@@ -3099,13 +3166,13 @@
         <v>21.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.59999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.1</v>
+        <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3135,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO15" t="n">
         <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
@@ -3162,7 +3229,7 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX15" t="n">
         <v>21</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" t="n">
         <v>39</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
-        <v>0.52</v>
+        <v>0.527</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
       </c>
       <c r="I16" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J16" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K16" t="n">
         <v>0.455</v>
@@ -3239,16 +3306,16 @@
         <v>19.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O16" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P16" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R16" t="n">
         <v>10.2</v>
@@ -3263,13 +3330,13 @@
         <v>20.4</v>
       </c>
       <c r="V16" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="W16" t="n">
         <v>8.1</v>
       </c>
       <c r="X16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y16" t="n">
         <v>4.1</v>
@@ -3287,19 +3354,19 @@
         <v>-0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
         <v>12</v>
@@ -3311,7 +3378,7 @@
         <v>18</v>
       </c>
       <c r="AL16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM16" t="n">
         <v>10</v>
@@ -3323,7 +3390,7 @@
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AQ16" t="n">
         <v>20</v>
@@ -3338,7 +3405,7 @@
         <v>28</v>
       </c>
       <c r="AU16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
@@ -3347,10 +3414,10 @@
         <v>5</v>
       </c>
       <c r="AX16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY16" t="n">
         <v>5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>6</v>
       </c>
       <c r="AZ16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3476,7 @@
         <v>36.5</v>
       </c>
       <c r="J17" t="n">
-        <v>82.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="K17" t="n">
         <v>0.443</v>
@@ -3418,16 +3485,16 @@
         <v>6.1</v>
       </c>
       <c r="M17" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O17" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="P17" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q17" t="n">
         <v>0.781</v>
@@ -3436,19 +3503,19 @@
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U17" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="V17" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W17" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X17" t="n">
         <v>3.7</v>
@@ -3457,16 +3524,16 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="AA17" t="n">
         <v>22.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="AD17" t="n">
         <v>2</v>
@@ -3502,10 +3569,10 @@
         <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3514,19 +3581,19 @@
         <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV17" t="n">
         <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -3663,10 +3730,10 @@
         <v>26</v>
       </c>
       <c r="AH18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AJ18" t="n">
         <v>7</v>
@@ -3675,10 +3742,10 @@
         <v>30</v>
       </c>
       <c r="AL18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN18" t="n">
         <v>22</v>
@@ -3687,10 +3754,10 @@
         <v>18</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
@@ -3702,10 +3769,10 @@
         <v>14</v>
       </c>
       <c r="AU18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F19" t="n">
         <v>44</v>
       </c>
       <c r="G19" t="n">
-        <v>0.413</v>
+        <v>0.405</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
@@ -3773,10 +3840,10 @@
         <v>35.8</v>
       </c>
       <c r="J19" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L19" t="n">
         <v>7.9</v>
@@ -3785,28 +3852,28 @@
         <v>21</v>
       </c>
       <c r="N19" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O19" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P19" t="n">
         <v>24.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R19" t="n">
         <v>10.3</v>
       </c>
       <c r="S19" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T19" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="U19" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V19" t="n">
         <v>13.1</v>
@@ -3818,22 +3885,22 @@
         <v>4.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.6</v>
+        <v>-2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
         <v>21</v>
@@ -3845,7 +3912,7 @@
         <v>21</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI19" t="n">
         <v>27</v>
@@ -3857,19 +3924,19 @@
         <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM19" t="n">
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AO19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
         <v>12</v>
@@ -3881,7 +3948,7 @@
         <v>21</v>
       </c>
       <c r="AT19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU19" t="n">
         <v>26</v>
@@ -3893,22 +3960,22 @@
         <v>22</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ19" t="n">
         <v>25</v>
       </c>
       <c r="BA19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -3937,64 +4004,64 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E20" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F20" t="n">
         <v>27</v>
       </c>
       <c r="G20" t="n">
-        <v>0.635</v>
+        <v>0.63</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
       </c>
       <c r="I20" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J20" t="n">
         <v>77.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
         <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
       <c r="O20" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P20" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q20" t="n">
         <v>0.8110000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S20" t="n">
         <v>30</v>
       </c>
       <c r="T20" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="U20" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="V20" t="n">
         <v>12.7</v>
       </c>
       <c r="W20" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X20" t="n">
         <v>4.3</v>
@@ -4003,22 +4070,22 @@
         <v>3.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="AC20" t="n">
         <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF20" t="n">
         <v>8</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
         <v>11</v>
@@ -4045,13 +4112,13 @@
         <v>13</v>
       </c>
       <c r="AN20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AO20" t="n">
         <v>20</v>
       </c>
       <c r="AP20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
@@ -4063,16 +4130,16 @@
         <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AU20" t="n">
         <v>28</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX20" t="n">
         <v>23</v>
@@ -4084,7 +4151,7 @@
         <v>9</v>
       </c>
       <c r="BA20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -4206,10 +4273,10 @@
         <v>23</v>
       </c>
       <c r="AG21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>6</v>
@@ -4227,13 +4294,13 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="n">
         <v>21</v>
       </c>
       <c r="AP21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ21" t="n">
         <v>10</v>
@@ -4254,7 +4321,7 @@
         <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>22</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
         <v>28</v>
@@ -4272,7 +4339,7 @@
         <v>4</v>
       </c>
       <c r="BC21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-5.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>25</v>
@@ -4391,7 +4458,7 @@
         <v>25</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
         <v>17</v>
@@ -4409,13 +4476,13 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO22" t="n">
         <v>6</v>
       </c>
       <c r="AP22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
         <v>9</v>
@@ -4436,7 +4503,7 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -4483,28 +4550,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E23" t="n">
         <v>55</v>
       </c>
       <c r="F23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>0.743</v>
+        <v>0.753</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J23" t="n">
         <v>78.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L23" t="n">
         <v>10.2</v>
@@ -4513,25 +4580,25 @@
         <v>26.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.386</v>
+        <v>0.388</v>
       </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P23" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.72</v>
+        <v>0.721</v>
       </c>
       <c r="R23" t="n">
         <v>9.9</v>
       </c>
       <c r="S23" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="T23" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U23" t="n">
         <v>19.5</v>
@@ -4540,7 +4607,7 @@
         <v>14.3</v>
       </c>
       <c r="W23" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X23" t="n">
         <v>5.3</v>
@@ -4552,16 +4619,16 @@
         <v>20.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.1</v>
+        <v>102.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4570,13 +4637,13 @@
         <v>3</v>
       </c>
       <c r="AG23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ23" t="n">
         <v>26</v>
@@ -4591,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4603,7 +4670,7 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4752,19 +4819,19 @@
         <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ24" t="n">
         <v>17</v>
       </c>
       <c r="AK24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4782,7 +4849,7 @@
         <v>6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR24" t="n">
         <v>2</v>
@@ -4791,7 +4858,7 @@
         <v>26</v>
       </c>
       <c r="AT24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU24" t="n">
         <v>22</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E25" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F25" t="n">
         <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>0.547</v>
+        <v>0.541</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4868,64 +4935,64 @@
         <v>81.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.505</v>
+        <v>0.504</v>
       </c>
       <c r="L25" t="n">
         <v>6.7</v>
       </c>
       <c r="M25" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.382</v>
+        <v>0.381</v>
       </c>
       <c r="O25" t="n">
         <v>20.1</v>
       </c>
       <c r="P25" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.748</v>
+        <v>0.751</v>
       </c>
       <c r="R25" t="n">
         <v>10.7</v>
       </c>
       <c r="S25" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T25" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U25" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V25" t="n">
         <v>15.7</v>
       </c>
       <c r="W25" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X25" t="n">
         <v>5.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>109.1</v>
+        <v>109</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4937,7 +5004,7 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>1</v>
@@ -4955,7 +5022,7 @@
         <v>19</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>5</v>
@@ -4964,10 +5031,10 @@
         <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
         <v>10</v>
@@ -4979,7 +5046,7 @@
         <v>3</v>
       </c>
       <c r="AV25" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AW25" t="n">
         <v>20</v>
@@ -4997,7 +5064,7 @@
         <v>6</v>
       </c>
       <c r="BB25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC25" t="n">
         <v>11</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E26" t="n">
         <v>47</v>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.644</v>
+        <v>0.635</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.463</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M26" t="n">
         <v>19.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
@@ -5077,13 +5144,13 @@
         <v>28.4</v>
       </c>
       <c r="T26" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U26" t="n">
         <v>20.4</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
         <v>6.7</v>
@@ -5095,34 +5162,34 @@
         <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA26" t="n">
         <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
         <v>23</v>
@@ -5140,13 +5207,13 @@
         <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,13 +5222,13 @@
         <v>28</v>
       </c>
       <c r="AT26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
         <v>17</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
@@ -5173,7 +5240,7 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA26" t="n">
         <v>12</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -5211,61 +5278,61 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E27" t="n">
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G27" t="n">
-        <v>0.216</v>
+        <v>0.219</v>
       </c>
       <c r="H27" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J27" t="n">
-        <v>81.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L27" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M27" t="n">
         <v>19.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.368</v>
+        <v>0.366</v>
       </c>
       <c r="O27" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="P27" t="n">
-        <v>26.1</v>
+        <v>25.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.804</v>
+        <v>0.803</v>
       </c>
       <c r="R27" t="n">
         <v>10</v>
       </c>
       <c r="S27" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="T27" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="U27" t="n">
         <v>19.8</v>
       </c>
       <c r="V27" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W27" t="n">
         <v>7.1</v>
@@ -5280,16 +5347,16 @@
         <v>23.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.9</v>
+        <v>100.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.1</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5304,7 +5371,7 @@
         <v>3</v>
       </c>
       <c r="AI27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="n">
         <v>14</v>
@@ -5319,7 +5386,7 @@
         <v>11</v>
       </c>
       <c r="AN27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5483,13 +5550,13 @@
         <v>6</v>
       </c>
       <c r="AH28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI28" t="n">
         <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
@@ -5519,10 +5586,10 @@
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -5575,55 +5642,55 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F29" t="n">
         <v>45</v>
       </c>
       <c r="G29" t="n">
-        <v>0.392</v>
+        <v>0.384</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J29" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L29" t="n">
         <v>5.9</v>
       </c>
       <c r="M29" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O29" t="n">
         <v>18.9</v>
       </c>
       <c r="P29" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.826</v>
+        <v>0.828</v>
       </c>
       <c r="R29" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="S29" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="T29" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="U29" t="n">
         <v>22.1</v>
@@ -5638,10 +5705,10 @@
         <v>4.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA29" t="n">
         <v>20.2</v>
@@ -5650,19 +5717,19 @@
         <v>98.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.8</v>
+        <v>-2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AE29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF29" t="n">
         <v>22</v>
       </c>
       <c r="AG29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH29" t="n">
         <v>14</v>
@@ -5689,7 +5756,7 @@
         <v>16</v>
       </c>
       <c r="AP29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5701,7 +5768,7 @@
         <v>11</v>
       </c>
       <c r="AT29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU29" t="n">
         <v>6</v>
@@ -5713,19 +5780,19 @@
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA29" t="n">
         <v>22</v>
       </c>
       <c r="BB29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BC29" t="n">
         <v>23</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>3.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF30" t="n">
         <v>10</v>
@@ -5847,7 +5914,7 @@
         <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI30" t="n">
         <v>5</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5874,13 +5941,13 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>11</v>
       </c>
       <c r="AS30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT30" t="n">
         <v>18</v>
@@ -5892,10 +5959,10 @@
         <v>22</v>
       </c>
       <c r="AW30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY30" t="n">
         <v>19</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E31" t="n">
         <v>17</v>
       </c>
       <c r="F31" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G31" t="n">
-        <v>0.224</v>
+        <v>0.227</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5978,7 +6045,7 @@
         <v>23.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
       <c r="R31" t="n">
         <v>11.8</v>
@@ -5990,7 +6057,7 @@
         <v>39.9</v>
       </c>
       <c r="U31" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V31" t="n">
         <v>13.9</v>
@@ -5999,25 +6066,25 @@
         <v>7.6</v>
       </c>
       <c r="X31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y31" t="n">
         <v>5.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>95.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.7</v>
+        <v>-7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6029,10 +6096,10 @@
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ31" t="n">
         <v>12</v>
@@ -6053,7 +6120,7 @@
         <v>25</v>
       </c>
       <c r="AP31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ31" t="n">
         <v>18</v>
@@ -6065,7 +6132,7 @@
         <v>30</v>
       </c>
       <c r="AT31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU31" t="n">
         <v>25</v>
@@ -6074,7 +6141,7 @@
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
         <v>24</v>
@@ -6086,7 +6153,7 @@
         <v>13</v>
       </c>
       <c r="BA31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-1-2008-09</t>
+          <t>2009-04-01</t>
         </is>
       </c>
     </row>
